--- a/បញ្ជីមន្រ្តី.xlsx
+++ b/បញ្ជីមន្រ្តី.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\Work\Organzied Work\Equipment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\Work\Organzied Work\Equipment\OSH-Equipment-System\OSH-Equipment-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9F7C37-4D29-486F-B935-E97F3EE54A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4867EE7C-45C2-465F-A655-C344F828D091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9900" yWindow="2720" windowWidth="15970" windowHeight="11570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="3610" windowWidth="15970" windowHeight="11570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="បញ្ជីមន្រ្តី" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="181">
   <si>
     <t>បច្ចុប្បន្នភាពមន្រ្ដីអធិការកិច្ចពេទ្យការងារ</t>
   </si>
@@ -576,592 +576,6 @@
   </si>
   <si>
     <t>011 545 432</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">មន្រ្ដីអធិការកិច្ចពេទ្យការងារមានតួនាទីជា៖ ប្រធានក្រុម </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFEE0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>០</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់ អនុប្រធានក្រុម </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFEE0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>៧</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់ សមាជិក </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFEE0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>៩</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>នាក់។</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- ភ្នំពេញ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១៦</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>នាក់។</t>
-    </r>
-  </si>
-  <si>
-    <t>សមាសភាពមន្រ្ដីអធិការកិច្ចពេទ្យការងារសម្រាប់ចុះនៅថ្នាក់ខេត្ត</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">មន្រ្ដីអធិការកិច្ចពេទ្យការងារមានតួនាទីជា៖ ប្រធានក្រុម </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFEE0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>៩</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់ អនុប្រធានក្រុម </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFEE0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>០</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់ សមាជិក </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFEE0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>២២</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>នាក់</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- កណ្ដាល </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>៣</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- កែប </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់		- ព្រៃវែង </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- ឧត្តរមានជ័យ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់
-- កំពង់ស្ពឺ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>៣</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- កំពង់ធំ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- ពោធិ៍សាត់ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- បន្ទាយមានជ័យ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់
-- ស្វាយរៀង </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>២</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- កោះកុង </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- កំពត </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់		- មណ្ឌលគិរី </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់
-- តាកែវ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>២</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់		- បាត់ដំបង </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- ត្បូងឃ្មុំ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- រតនគិរី </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់
-- ព្រះសីហនុ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>២</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- កំពង់ចាម </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- ព្រះវិហារ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- សៀមរាប </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់
-- ប៉ៃលិន </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- កំពង់ឆ្នាំង </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់	- ក្រចេះ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t xml:space="preserve">នាក់		-ស្ទឹងត្រែង </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>១</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Khmer OS Siemreap"/>
-      </rPr>
-      <t>នាក់</t>
-    </r>
   </si>
 </sst>
 </file>
@@ -1171,7 +585,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-12000453]0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1223,24 +637,6 @@
       <color rgb="FFFF0000"/>
       <name val="Khmer OS Siemreap-Kh Auto"/>
     </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Khmer OS Siemreap"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FFEE0000"/>
-      <name val="Khmer OS Siemreap"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Khmer OS Siemreap"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1262,7 +658,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1320,98 +716,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1463,40 +773,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1521,6 +801,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="បញ្ជីមន្រ្តី"/>
@@ -1892,1459 +1173,1340 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="A2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
     </row>
     <row r="3" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="7"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="7">
         <v>2</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="9" t="s">
+      <c r="D5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="10"/>
+      <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>3</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="D6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="7"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="7">
         <v>4</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="9" t="s">
+      <c r="D7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="10"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>5</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="D8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="7"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+      <c r="A9" s="2">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="7">
         <v>6</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="D9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="10"/>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+      <c r="A10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>7</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="6" t="s">
+      <c r="D10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="7"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
+      <c r="A11" s="2">
         <v>8</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="7">
         <v>8</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I11" s="10"/>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>9</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="D12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="7"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="4">
+      <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="7">
         <v>10</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="D13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="I13" s="10"/>
+      <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="4">
+      <c r="A14" s="2">
         <v>11</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
         <v>11</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="D14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="7"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="4">
-        <v>12</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="A15" s="2">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="9">
-        <v>12</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="C15" s="7">
+        <v>12</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="10"/>
+      <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="4">
-        <v>13</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="A16" s="2">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="6">
-        <v>13</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="C16" s="4">
+        <v>13</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="7"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="4">
+      <c r="A17" s="2">
         <v>14</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="7">
         <v>14</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="D17" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="10"/>
+      <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="4">
+      <c r="A18" s="2">
         <v>15</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="4">
         <v>15</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="D18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I18" s="7"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="11">
+      <c r="A19" s="9">
         <v>16</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="7">
         <v>16</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="9" t="s">
+      <c r="D19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I19" s="10"/>
+      <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="4">
+      <c r="A20" s="2">
         <v>17</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="9">
-        <v>1</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I20" s="10"/>
+      <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="4">
+      <c r="A21" s="2">
         <v>18</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="4">
         <v>2</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="6" t="s">
+      <c r="D21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I21" s="7"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="4">
+      <c r="A22" s="2">
         <v>19</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="7">
         <v>3</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="9" t="s">
+      <c r="D22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I22" s="10"/>
+      <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="4">
+      <c r="A23" s="2">
         <v>20</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="6">
-        <v>1</v>
-      </c>
-      <c r="D23" s="6" t="s">
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="I23" s="6"/>
+      <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="4">
+      <c r="A24" s="2">
         <v>21</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="7">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="D24" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="I24" s="9"/>
+      <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="4">
+      <c r="A25" s="2">
         <v>22</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="4">
         <v>3</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="6" t="s">
+      <c r="D25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="I25" s="6"/>
+      <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="4">
+      <c r="A26" s="2">
         <v>23</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="14">
-        <v>1</v>
-      </c>
-      <c r="D26" s="9" t="s">
+      <c r="C26" s="12">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I26" s="9"/>
+      <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="4">
+      <c r="A27" s="2">
         <v>24</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13">
         <v>2</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="6" t="s">
+      <c r="D27" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="I27" s="6"/>
+      <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="4">
+      <c r="A28" s="2">
         <v>25</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="12">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I28" s="9"/>
+      <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="4">
+      <c r="A29" s="2">
         <v>26</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="6" t="s">
+      <c r="C29" s="13">
+        <v>1</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="I29" s="6"/>
+      <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="4">
+      <c r="A30" s="2">
         <v>27</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="16">
-        <v>1</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="I30" s="10"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="4">
+      <c r="A31" s="2">
         <v>28</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="15">
         <v>2</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="6" t="s">
+      <c r="D31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I31" s="7"/>
+      <c r="I31" s="5"/>
     </row>
     <row r="32" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="4">
+      <c r="A32" s="2">
         <v>29</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="16">
-        <v>1</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="C32" s="14">
+        <v>1</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="I32" s="10"/>
+      <c r="I32" s="8"/>
     </row>
     <row r="33" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="4">
+      <c r="A33" s="2">
         <v>30</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="17">
-        <v>1</v>
-      </c>
-      <c r="D33" s="7" t="s">
+      <c r="C33" s="15">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I33" s="7"/>
+      <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="4">
+      <c r="A34" s="2">
         <v>31</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="16">
-        <v>1</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="18" t="s">
+      <c r="C34" s="14">
+        <v>1</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="G34" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="I34" s="10"/>
+      <c r="I34" s="8"/>
     </row>
     <row r="35" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="4">
+      <c r="A35" s="2">
         <v>32</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C35" s="17">
-        <v>1</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="19" t="s">
+      <c r="C35" s="15">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="I35" s="7"/>
+      <c r="I35" s="5"/>
     </row>
     <row r="36" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="4">
+      <c r="A36" s="2">
         <v>33</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="16">
-        <v>1</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="10" t="s">
+      <c r="C36" s="14">
+        <v>1</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F36" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="I36" s="10"/>
+      <c r="I36" s="8"/>
     </row>
     <row r="37" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="4">
+      <c r="A37" s="2">
         <v>34</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C37" s="17">
-        <v>1</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="6" t="s">
+      <c r="C37" s="15">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="I37" s="7"/>
+      <c r="I37" s="5"/>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="4">
+      <c r="A38" s="2">
         <v>35</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C38" s="16">
-        <v>1</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="18" t="s">
+      <c r="C38" s="14">
+        <v>1</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="I38" s="10"/>
+      <c r="I38" s="8"/>
     </row>
     <row r="39" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="4">
+      <c r="A39" s="2">
         <v>36</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C39" s="17">
-        <v>1</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="7" t="s">
+      <c r="C39" s="15">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="G39" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="I39" s="7"/>
+      <c r="I39" s="5"/>
     </row>
     <row r="40" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="4">
+      <c r="A40" s="2">
         <v>37</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C40" s="16">
-        <v>1</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="9" t="s">
+      <c r="C40" s="14">
+        <v>1</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I40" s="10"/>
+      <c r="I40" s="8"/>
     </row>
     <row r="41" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="4">
+      <c r="A41" s="2">
         <v>38</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C41" s="17">
-        <v>1</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="6" t="s">
+      <c r="C41" s="15">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="G41" s="7" t="s">
+      <c r="G41" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="I41" s="7"/>
+      <c r="I41" s="5"/>
     </row>
     <row r="42" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="4">
+      <c r="A42" s="2">
         <v>39</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="16">
-        <v>1</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="9" t="s">
+      <c r="C42" s="14">
+        <v>1</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="I42" s="10"/>
+      <c r="I42" s="8"/>
     </row>
     <row r="43" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="4">
+      <c r="A43" s="2">
         <v>40</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C43" s="17">
-        <v>1</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="7" t="s">
+      <c r="C43" s="15">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="G43" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="I43" s="7"/>
+      <c r="I43" s="5"/>
     </row>
     <row r="44" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="4">
+      <c r="A44" s="2">
         <v>41</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C44" s="16">
-        <v>1</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="9" t="s">
+      <c r="C44" s="14">
+        <v>1</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="G44" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="I44" s="10"/>
+      <c r="I44" s="8"/>
     </row>
     <row r="45" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="4">
+      <c r="A45" s="2">
         <v>42</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C45" s="17">
-        <v>1</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="7" t="s">
+      <c r="C45" s="15">
+        <v>1</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="G45" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="I45" s="7"/>
+      <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="4">
+      <c r="A46" s="2">
         <v>43</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C46" s="16">
-        <v>1</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="9" t="s">
+      <c r="C46" s="14">
+        <v>1</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="G46" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H46" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="I46" s="10"/>
+      <c r="I46" s="8"/>
     </row>
     <row r="47" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="4">
+      <c r="A47" s="2">
         <v>44</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C47" s="17">
-        <v>1</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" s="19" t="s">
+      <c r="C47" s="15">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="G47" s="7" t="s">
+      <c r="G47" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="I47" s="7"/>
+      <c r="I47" s="5"/>
     </row>
     <row r="48" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="4">
+      <c r="A48" s="2">
         <v>45</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C48" s="16">
-        <v>1</v>
-      </c>
-      <c r="D48" s="10" t="s">
+      <c r="C48" s="14">
+        <v>1</v>
+      </c>
+      <c r="D48" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="9" t="s">
+      <c r="E48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="G48" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H48" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="I48" s="10"/>
+      <c r="I48" s="8"/>
     </row>
     <row r="49" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="4">
+      <c r="A49" s="2">
         <v>46</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C49" s="17">
-        <v>1</v>
-      </c>
-      <c r="D49" s="7" t="s">
+      <c r="C49" s="15">
+        <v>1</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="6" t="s">
+      <c r="E49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="G49" s="7" t="s">
+      <c r="G49" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="I49" s="7"/>
+      <c r="I49" s="5"/>
     </row>
     <row r="50" spans="1:9" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="11">
+      <c r="A50" s="9">
         <v>47</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C50" s="16">
-        <v>1</v>
-      </c>
-      <c r="D50" s="10" t="s">
+      <c r="C50" s="14">
+        <v>1</v>
+      </c>
+      <c r="D50" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="E50" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="9" t="s">
+      <c r="E50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="H50" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="I50" s="10"/>
-    </row>
-    <row r="59" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="60" spans="1:9" ht="24.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
-      <c r="I60" s="22"/>
-    </row>
-    <row r="61" spans="1:9" ht="24.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="25"/>
-    </row>
-    <row r="62" spans="1:9" ht="24.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-    </row>
-    <row r="64" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="28"/>
-    </row>
-    <row r="65" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="B65" s="30"/>
-      <c r="C65" s="30"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="30"/>
-      <c r="F65" s="30"/>
-      <c r="G65" s="30"/>
-      <c r="H65" s="30"/>
-      <c r="I65" s="31"/>
-    </row>
-    <row r="66" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="29"/>
-      <c r="B66" s="30"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
-      <c r="H66" s="30"/>
-      <c r="I66" s="31"/>
-    </row>
-    <row r="67" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="29"/>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="31"/>
-    </row>
-    <row r="68" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="29"/>
-      <c r="B68" s="30"/>
-      <c r="C68" s="30"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="31"/>
-    </row>
-    <row r="69" spans="1:9" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="29"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="31"/>
-    </row>
-    <row r="70" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="23"/>
-      <c r="B70" s="24"/>
-      <c r="C70" s="24"/>
-      <c r="D70" s="24"/>
-      <c r="E70" s="24"/>
-      <c r="F70" s="24"/>
-      <c r="G70" s="24"/>
-      <c r="H70" s="24"/>
-      <c r="I70" s="25"/>
-    </row>
+      <c r="I50" s="8"/>
+    </row>
+    <row r="64" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="26.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="26.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="25.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A65:I70"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A60:I60"/>
-    <mergeCell ref="A61:I61"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="A64:I64"/>
   </mergeCells>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="56" orientation="portrait" r:id="rId1"/>
